--- a/Config/Excels/Local/L-Localization-成就.xlsx
+++ b/Config/Excels/Local/L-Localization-成就.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18530"/>
+    <workbookView windowHeight="18450"/>
   </bookViews>
   <sheets>
     <sheet name="成就" sheetId="9" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45">
   <si>
     <t>##var</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>##group</t>
   </si>
   <si>
     <t>##</t>
@@ -160,11 +157,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,12 +198,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF9C0006"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF161616"/>
@@ -215,13 +206,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -242,6 +226,73 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -251,43 +302,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,40 +332,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -348,45 +363,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -401,7 +385,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,49 +421,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,127 +535,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,11 +622,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,27 +661,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -697,8 +673,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -735,9 +711,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -747,10 +725,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -759,137 +737,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -915,25 +893,19 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -942,7 +914,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1273,8 +1245,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <dimension ref="A1:Q17"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="8.66666666666667" style="3"/>
     <col min="3" max="3" width="35.75" style="3" customWidth="1"/>
@@ -1283,7 +1255,7 @@
     <col min="18" max="16384" width="8.66666666666667" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="36" spans="1:17">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1311,387 +1283,340 @@
       <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="18" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="O1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="P1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="Q1" s="18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
+    <row r="2" s="1" customFormat="1" ht="18" spans="1:17">
+      <c r="A2" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
+      <c r="C2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A3" s="8" t="s">
-        <v>17</v>
+    <row r="3" s="1" customFormat="1" ht="18" spans="1:17">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="B3" s="5"/>
-      <c r="C3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>18</v>
+      <c r="C3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="18" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
+    <row r="4" s="2" customFormat="1" ht="15.75" spans="1:17">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="P5" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q5" s="20" t="s">
-        <v>35</v>
-      </c>
+    <row r="5" s="2" customFormat="1" ht="26" customHeight="1" spans="1:17">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:1">
-      <c r="A6" s="11" t="s">
-        <v>20</v>
+    <row r="6" s="2" customFormat="1" ht="15" spans="1:4">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:17">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
+    <row r="7" s="2" customFormat="1" ht="15" spans="1:4">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="26" customHeight="1" spans="1:17">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
+    <row r="8" s="2" customFormat="1" ht="15" spans="1:4">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>41</v>
-      </c>
+    <row r="9" s="2" customFormat="1" spans="1:4">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
     </row>
-    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>43</v>
-      </c>
+    <row r="10" s="2" customFormat="1" ht="15" spans="1:4">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
     </row>
-    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>45</v>
-      </c>
+    <row r="11" s="2" customFormat="1" ht="15" spans="1:4">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:4">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
+    <row r="12" s="3" customFormat="1" spans="1:17">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
     </row>
-    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
+    <row r="13" s="3" customFormat="1" spans="1:17">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
     </row>
-    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
+    <row r="14" s="3" customFormat="1" spans="1:17">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
     </row>
     <row r="15" s="3" customFormat="1" spans="1:17">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:17">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:17">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:17">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:17">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:17">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
